--- a/site_pelada/pelada_ranking.xlsx
+++ b/site_pelada/pelada_ranking.xlsx
@@ -64,7 +64,7 @@
     <t>Gabriel F.</t>
   </si>
   <si>
-    <t>Grab</t>
+    <t>Gab</t>
   </si>
   <si>
     <t>Gui</t>

--- a/site_pelada/pelada_ranking.xlsx
+++ b/site_pelada/pelada_ranking.xlsx
@@ -85,7 +85,7 @@
     <t>João Pedro</t>
   </si>
   <si>
-    <t>Kel</t>
+    <t>Kelvyn Eduardo</t>
   </si>
   <si>
     <t>Matheus M</t>
